--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:44</t>
+    <t xml:space="preserve">2026-09-09 22:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:32</t>
+    <t xml:space="preserve">2026-09-12 19:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:48</t>
+    <t xml:space="preserve">2026-09-24 00:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:26</t>
+    <t xml:space="preserve">2026-09-27 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.41</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.35</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.32</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.16</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1.15</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-3.38</v>
+        <v>-33.75</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-7.74</v>
+        <v>-77.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:08</t>
+    <t xml:space="preserve">2026-10-01 20:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:55</t>
+    <t xml:space="preserve">2026-10-02 13:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:24</t>
+    <t xml:space="preserve">2026-10-05 08:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
